--- a/artfynd/A 15665-2022 artfynd.xlsx
+++ b/artfynd/A 15665-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15665-2022 artfynd.xlsx
+++ b/artfynd/A 15665-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1871522</v>
+        <v>424254</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543218.3351293887</v>
+        <v>543230</v>
       </c>
       <c r="R2" t="n">
-        <v>7034239.3934711</v>
+        <v>7034126</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>424254</v>
+        <v>97186889</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,13 +811,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543229.7276641274</v>
+        <v>543256</v>
       </c>
       <c r="R3" t="n">
-        <v>7034126.277698853</v>
+        <v>7034194</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Ecogain</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97186894</v>
+        <v>97186895</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543314.020994048</v>
+        <v>543311</v>
       </c>
       <c r="R4" t="n">
-        <v>7034092.496905818</v>
+        <v>7034100</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,55 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97186888</v>
+        <v>97186893</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543189.411226921</v>
+        <v>543346</v>
       </c>
       <c r="R5" t="n">
-        <v>7034157.072554859</v>
+        <v>7034111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1046,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97186893</v>
+        <v>1871522</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543346.948012505</v>
+        <v>543218</v>
       </c>
       <c r="R6" t="n">
-        <v>7034110.852018611</v>
+        <v>7034239</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-09-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,35 +1164,30 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97186898</v>
+        <v>97186890</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543230.1030237504</v>
+        <v>543345</v>
       </c>
       <c r="R7" t="n">
-        <v>7034098.524338376</v>
+        <v>7034156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1248,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97186895</v>
+        <v>97186898</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543311.2344980424</v>
+        <v>543230</v>
       </c>
       <c r="R8" t="n">
-        <v>7034099.622656856</v>
+        <v>7034099</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,19 +1349,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97186897</v>
+        <v>97186888</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,34 +1393,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543255.2165920393</v>
+        <v>543190</v>
       </c>
       <c r="R9" t="n">
-        <v>7034097.968655976</v>
+        <v>7034157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,19 +1455,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,12 +1491,7 @@
         <v>97186896</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543263.4060952081</v>
+        <v>543263</v>
       </c>
       <c r="R10" t="n">
-        <v>7034089.125102429</v>
+        <v>7034089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,19 +1561,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,50 +1594,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97186889</v>
+        <v>97186891</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Borgvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543256.1613881311</v>
+        <v>543360</v>
       </c>
       <c r="R11" t="n">
-        <v>7034193.791844913</v>
+        <v>7034175</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,19 +1666,14 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst en tupp och en höna, i hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,37 +1704,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97186890</v>
+        <v>97186897</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543345.4262822304</v>
+        <v>543256</v>
       </c>
       <c r="R12" t="n">
-        <v>7034156.945946816</v>
+        <v>7034098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,19 +1772,9 @@
           <t>2021-10-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 15665-2022 artfynd.xlsx
+++ b/artfynd/A 15665-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/424254</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186889</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186895</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186893</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186890</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186898</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186891</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,8 +1857,26 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97186897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>